--- a/book_data/Fitness.xlsx
+++ b/book_data/Fitness.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edmundlskoviak/Library/Mobile Documents/com~apple~CloudDocs/Data Sets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028DD6FF-16CB-E84F-8A34-1C3577A5C44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E833AD36-328D-4545-A88F-39DB5F29A900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2960" yWindow="2260" windowWidth="28200" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3467,9 +3467,33 @@
       </c>
     </row>
     <row r="126" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="1"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
+      <c r="A126" s="1">
+        <v>45646</v>
+      </c>
+      <c r="B126" s="2">
+        <v>180.3</v>
+      </c>
+      <c r="C126" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="D126">
+        <v>1091</v>
+      </c>
+      <c r="E126">
+        <v>435</v>
+      </c>
+      <c r="I126">
+        <v>260</v>
+      </c>
+      <c r="M126">
+        <v>14074</v>
+      </c>
+      <c r="N126">
+        <v>5.7</v>
+      </c>
+      <c r="O126" s="3">
+        <v>12</v>
+      </c>
     </row>
     <row r="127" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>

--- a/book_data/Fitness.xlsx
+++ b/book_data/Fitness.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11213"/>
   <workbookPr showInkAnnotation="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72E78CA5-BD4A-3048-B4CC-C059E9479A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5745B120-FD88-1740-8477-F515E0396A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5420,21 +5420,33 @@
       </c>
     </row>
     <row r="131" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="4"/>
+      <c r="A131" s="4">
+        <v>45651</v>
+      </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
-      <c r="D131" s="8"/>
+      <c r="D131" s="8">
+        <v>659</v>
+      </c>
       <c r="E131" s="8"/>
       <c r="F131" s="7"/>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
-      <c r="I131" s="8"/>
+      <c r="I131" s="8">
+        <v>292</v>
+      </c>
       <c r="J131" s="8"/>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
-      <c r="M131" s="8"/>
-      <c r="N131" s="8"/>
-      <c r="O131" s="8"/>
+      <c r="M131" s="8">
+        <v>12581</v>
+      </c>
+      <c r="N131" s="8">
+        <v>5.48</v>
+      </c>
+      <c r="O131" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>

--- a/book_data/Fitness.xlsx
+++ b/book_data/Fitness.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11213"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr showInkAnnotation="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5745B120-FD88-1740-8477-F515E0396A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edmundlskoviak/Documents/repos/pyspark-playground/book_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73DF4B6-30EF-2A47-9931-B1601E4B6396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="21380" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -150,19 +155,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1294,13 +1298,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O1031"/>
-  <sheetFormatPr defaultColWidth="14.52734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5078125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.47265625" style="1" customWidth="1"/>
-    <col min="4" max="15" width="8.609375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.52734375" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.52734375" style="1"/>
+    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.5" style="1" customWidth="1"/>
+    <col min="4" max="15" width="8.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.5" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5449,55 +5453,101 @@
       </c>
     </row>
     <row r="132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="4"/>
+      <c r="A132" s="4">
+        <v>45652</v>
+      </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
-      <c r="D132" s="8"/>
+      <c r="D132" s="8">
+        <v>706</v>
+      </c>
       <c r="E132" s="8"/>
       <c r="F132" s="7"/>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
-      <c r="I132" s="8"/>
+      <c r="I132" s="8">
+        <v>275</v>
+      </c>
       <c r="J132" s="8"/>
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
-      <c r="M132" s="8"/>
-      <c r="N132" s="8"/>
-      <c r="O132" s="8"/>
+      <c r="M132" s="8">
+        <v>14167</v>
+      </c>
+      <c r="N132" s="8">
+        <v>5.89</v>
+      </c>
+      <c r="O132" s="8">
+        <v>15</v>
+      </c>
     </row>
     <row r="133" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="4"/>
+      <c r="A133" s="4">
+        <v>45653</v>
+      </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="7"/>
+      <c r="D133" s="8">
+        <v>1116</v>
+      </c>
+      <c r="E133" s="8">
+        <v>191</v>
+      </c>
+      <c r="F133" s="7">
+        <v>205</v>
+      </c>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
-      <c r="I133" s="8"/>
+      <c r="I133" s="8">
+        <v>167</v>
+      </c>
       <c r="J133" s="8"/>
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
-      <c r="M133" s="8"/>
-      <c r="N133" s="8"/>
-      <c r="O133" s="8"/>
+      <c r="M133" s="8">
+        <v>15634</v>
+      </c>
+      <c r="N133" s="8">
+        <v>6.48</v>
+      </c>
+      <c r="O133" s="8">
+        <v>12</v>
+      </c>
     </row>
     <row r="134" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="4"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
+      <c r="A134" s="4">
+        <v>45654</v>
+      </c>
+      <c r="B134" s="5">
+        <v>177.4</v>
+      </c>
+      <c r="C134" s="5">
+        <v>24.6</v>
+      </c>
+      <c r="D134" s="8">
+        <v>1173</v>
+      </c>
+      <c r="E134" s="8">
+        <v>560</v>
+      </c>
       <c r="F134" s="7"/>
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
-      <c r="I134" s="8"/>
+      <c r="I134" s="8">
+        <v>219</v>
+      </c>
       <c r="J134" s="8"/>
       <c r="K134" s="8"/>
       <c r="L134" s="8"/>
-      <c r="M134" s="8"/>
-      <c r="N134" s="8"/>
-      <c r="O134" s="8"/>
+      <c r="M134" s="8">
+        <v>16077</v>
+      </c>
+      <c r="N134" s="8">
+        <v>6.67</v>
+      </c>
+      <c r="O134" s="8">
+        <v>12</v>
+      </c>
     </row>
     <row r="135" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
@@ -20760,12 +20810,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="10.89453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="10.89453125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="11.703125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="10.89453125" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="10.89453125" style="10"/>
+    <col min="1" max="5" width="10.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -20804,7 +20854,7 @@
       <c r="E2" s="6">
         <v>0.99</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>0.68070477009024499</v>
       </c>
     </row>
@@ -20824,7 +20874,7 @@
       <c r="E3" s="6">
         <v>0.85</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>0.66995073891625601</v>
       </c>
     </row>
@@ -20844,7 +20894,7 @@
       <c r="E4" s="6">
         <v>1.62</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="10">
         <v>0.68318397469688996</v>
       </c>
     </row>
@@ -20864,7 +20914,7 @@
       <c r="E5" s="6">
         <v>1.74</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="10">
         <v>0.70821673874332203</v>
       </c>
     </row>
@@ -20884,7 +20934,7 @@
       <c r="E6" s="6">
         <v>2.59</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>0.69239766081871301</v>
       </c>
     </row>
